--- a/ehs_courses_matched.xlsx
+++ b/ehs_courses_matched.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2326" uniqueCount="619">
   <si>
     <t>Course Number</t>
   </si>
@@ -529,6 +529,9 @@
     <t>The purpose of the course is to introduce the systematic and scientific study of the behavior and mental processes of human beings and other animals. Included is a consideration of the psychological facts, principles, and phenomena associated with each of the major subfields within psychology. Students also learn about the ethics and methods psychologists use in their science and practice. Homework for this course is an invaluable tool used to introduce, reinforce, and help with comprehension with respect to course material.</t>
   </si>
   <si>
+    <t>797251A</t>
+  </si>
+  <si>
     <t>AP Calculus AB</t>
   </si>
   <si>
@@ -541,6 +544,9 @@
     <t>Students learn the basic Calculus concepts presented in AB. This course covers the topics of the AB exam, and will prepare students for the more rigorous second level of Calculus. Topics of study include but are not limited to analysis of graphs, limits, continuity, derivatives and their applications, definite and indefinite integrals and their applications, and the Fundamental Theorem of Calculus. This course meets the Advanced Placement curriculum requirements. In this class students explore and understand Calculus concepts graphically, numerically, analytically, and verbally. The goal of this course is to give students a deeper and more thorough understanding of mathematics based on Calculus. This goal of this course should better prepare students for the rigorous mathematics courses of college. Students will take the AP Calculus AB test at the end of the year and may earn college credit.</t>
   </si>
   <si>
+    <t>797251B</t>
+  </si>
+  <si>
     <t>AP Calculus AB (for those graduating after 2028)</t>
   </si>
   <si>
@@ -556,6 +562,9 @@
     <t>Students should have successfully completed AP Calculus AB.</t>
   </si>
   <si>
+    <t>(797251A, 797251B)</t>
+  </si>
+  <si>
     <t>This is a continuation course of Calculus AB. Students will review the basic Calculus concepts presented in AB in a condensed and intensified level and then learn additional concepts such as the Calculus involving parametric, polar, and vector functions; power, Taylor, and Maclaurin series; and analysis of the different series. This course covers the topics on the BC exam, and will prepare students for the third level of Calculus offered at a university. This is an extremely rigorous course meeting the Advanced Placement curriculum requirements. Students continue to explore and understand Calculus concepts graphically, numerically, analytically, and verbally. The goal of this course is to continue to give students a deeper and more thorough understanding of mathematics based on Calculus. This goal of this course should better prepare students for the rigorous mathematics courses of college. The students will take the AP Calculus BC test at the end of the year and may earn college credit.</t>
   </si>
   <si>
@@ -910,7 +919,7 @@
     <t>20-40 minutes a day, 2-3 hrs a week; may include lecture videos, practice assessments, labs, and projects. Additional time may need to be spent studying.</t>
   </si>
   <si>
-    <t>Team Sports (Year)</t>
+    <t>Team Sports (Year - 0 period)</t>
   </si>
   <si>
     <t>Successfully completed 9 th grade PE, teacher recommendation</t>
@@ -919,6 +928,9 @@
     <t>This course builds on the basic foundation of the ninth grade core program. The goal of this course is to provide students with an opportunity to choose lifetime activities and increase their skill proficiency, strength, flexibility and conceptual learning specific to each instructional unit. These activities include football, ultimate frisbee, soccer, softball, basketball, volleyball, hockey, and lacrosse.</t>
   </si>
   <si>
+    <t>Team Sports (Semester - 0 period)</t>
+  </si>
+  <si>
     <t>Introduction to Weight Lifting</t>
   </si>
   <si>
@@ -1807,13 +1819,10 @@
     <t>5-10 minutes per day, 5 days per week, plus additional time for performance test preparation</t>
   </si>
   <si>
-    <t>Team Sports (0 Period)</t>
+    <t>Introduction to Weight Lifting (0 Period)</t>
   </si>
   <si>
     <t>Successfully completed 9th grade PE</t>
-  </si>
-  <si>
-    <t>Introduction to Weight Lifting (0 Period)</t>
   </si>
   <si>
     <t xml:space="preserve">This course introduces students to a variety of training programs.  Students will focus on areas related to muscular strength, muscular endurance, flexibility, and use the information obtained in testing to develop an effective training program. Students do not need to have any prior training or knowledge as it pertains to weight lifting to take this course. A variety of training techniques will be introduced along with proper technique, benefits of various types of training systems, spotting techniques, and the science behind effective training.  </t>
@@ -3126,8 +3135,8 @@
       <c r="E23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F23" s="1">
-        <v>753681.0</v>
+      <c r="F23" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>19</v>
@@ -3170,8 +3179,8 @@
       <c r="E24" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="1">
-        <v>753681.0</v>
+      <c r="F24" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>19</v>
@@ -3214,8 +3223,8 @@
       <c r="E25" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="F25" s="1">
-        <v>753681.0</v>
+      <c r="F25" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>19</v>
@@ -3258,8 +3267,8 @@
       <c r="E26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F26" s="1">
-        <v>753681.0</v>
+      <c r="F26" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>19</v>
@@ -3302,8 +3311,8 @@
       <c r="E27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F27" s="1">
-        <v>753681.0</v>
+      <c r="F27" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>19</v>
@@ -3434,8 +3443,8 @@
       <c r="E30" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F30" s="1">
-        <v>753681.0</v>
+      <c r="F30" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>19</v>
@@ -3478,8 +3487,8 @@
       <c r="E31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F31" s="1">
-        <v>753681.0</v>
+      <c r="F31" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>19</v>
@@ -3522,8 +3531,8 @@
       <c r="E32" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F32" s="1">
-        <v>753681.0</v>
+      <c r="F32" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>19</v>
@@ -3566,8 +3575,8 @@
       <c r="E33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F33" s="1">
-        <v>753681.0</v>
+      <c r="F33" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>19</v>
@@ -4431,11 +4440,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2">
-        <v>797251.0</v>
+      <c r="A53" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C53" s="1">
         <v>10.0</v>
@@ -4444,10 +4453,10 @@
         <v>16</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>19</v>
@@ -4459,7 +4468,7 @@
         <v>161</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>132</v>
@@ -4475,11 +4484,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2">
-        <v>797251.0</v>
+      <c r="A54" s="2" t="s">
+        <v>177</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C54" s="1">
         <v>10.0</v>
@@ -4488,10 +4497,10 @@
         <v>16</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>19</v>
@@ -4503,7 +4512,7 @@
         <v>161</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K54" s="1" t="s">
         <v>132</v>
@@ -4526,7 +4535,7 @@
         <v>797252.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C55" s="1">
         <v>10.0</v>
@@ -4535,10 +4544,10 @@
         <v>16</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F55" s="1">
-        <v>797251.0</v>
+        <v>182</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>19</v>
@@ -4550,7 +4559,7 @@
         <v>161</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>132</v>
@@ -4570,7 +4579,7 @@
         <v>797255.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C56" s="1">
         <v>10.0</v>
@@ -4579,10 +4588,10 @@
         <v>16</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>19</v>
@@ -4594,10 +4603,10 @@
         <v>161</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>50</v>
@@ -4614,7 +4623,7 @@
         <v>720000.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C57" s="1">
         <v>10.0</v>
@@ -4623,7 +4632,7 @@
         <v>16</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>19</v>
@@ -4638,10 +4647,10 @@
         <v>21</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L57" s="1">
         <v>9.0</v>
@@ -4658,7 +4667,7 @@
         <v>720010.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C58" s="1">
         <v>10.0</v>
@@ -4667,7 +4676,7 @@
         <v>16</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F58" s="1">
         <v>720000.0</v>
@@ -4682,10 +4691,10 @@
         <v>21</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L58" s="1">
         <v>10.0</v>
@@ -4702,7 +4711,7 @@
         <v>797081.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C59" s="1">
         <v>10.0</v>
@@ -4711,10 +4720,10 @@
         <v>16</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>19</v>
@@ -4726,10 +4735,10 @@
         <v>161</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>45</v>
@@ -4746,7 +4755,7 @@
         <v>797086.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C60" s="1">
         <v>10.0</v>
@@ -4755,7 +4764,7 @@
         <v>16</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F60" s="1">
         <v>797060.0</v>
@@ -4770,10 +4779,10 @@
         <v>161</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>45</v>
@@ -4790,7 +4799,7 @@
         <v>797175.0</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C61" s="1">
         <v>10.0</v>
@@ -4799,10 +4808,10 @@
         <v>16</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>19</v>
@@ -4814,10 +4823,10 @@
         <v>161</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="L61" s="1" t="s">
         <v>45</v>
@@ -4834,7 +4843,7 @@
         <v>797174.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C62" s="1">
         <v>10.0</v>
@@ -4843,10 +4852,10 @@
         <v>16</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>19</v>
@@ -4858,10 +4867,10 @@
         <v>161</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="L62" s="1" t="s">
         <v>50</v>
@@ -4878,7 +4887,7 @@
         <v>720020.0</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C63" s="1">
         <v>10.0</v>
@@ -4887,7 +4896,7 @@
         <v>16</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F63" s="1">
         <v>720010.0</v>
@@ -4902,10 +4911,10 @@
         <v>21</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L63" s="1">
         <v>11.0</v>
@@ -4922,7 +4931,7 @@
         <v>720030.0</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C64" s="1">
         <v>10.0</v>
@@ -4931,7 +4940,7 @@
         <v>16</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F64" s="1">
         <v>720020.0</v>
@@ -4946,10 +4955,10 @@
         <v>21</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="L64" s="1">
         <v>12.0</v>
@@ -4966,7 +4975,7 @@
         <v>717250.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C65" s="1">
         <v>10.0</v>
@@ -4990,7 +4999,7 @@
         <v>21</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="K65" s="1" t="s">
         <v>19</v>
@@ -5010,7 +5019,7 @@
         <v>710414.0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C66" s="1">
         <v>10.0</v>
@@ -5034,10 +5043,10 @@
         <v>121</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>45</v>
@@ -5054,7 +5063,7 @@
         <v>710417.0</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C67" s="1">
         <v>10.0</v>
@@ -5063,7 +5072,7 @@
         <v>16</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F67" s="1">
         <v>710414.0</v>
@@ -5078,10 +5087,10 @@
         <v>121</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>45</v>
@@ -5098,7 +5107,7 @@
         <v>717251.0</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C68" s="1">
         <v>10.0</v>
@@ -5107,7 +5116,7 @@
         <v>16</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="F68" s="1">
         <v>717250.0</v>
@@ -5122,10 +5131,10 @@
         <v>21</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>31</v>
@@ -5142,7 +5151,7 @@
         <v>717101.0</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C69" s="1">
         <v>5.0</v>
@@ -5151,7 +5160,7 @@
         <v>82</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>19</v>
@@ -5166,7 +5175,7 @@
         <v>21</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>19</v>
@@ -5186,7 +5195,7 @@
         <v>717100.0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C70" s="1">
         <v>10.0</v>
@@ -5195,7 +5204,7 @@
         <v>16</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>19</v>
@@ -5210,7 +5219,7 @@
         <v>21</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>19</v>
@@ -5230,7 +5239,7 @@
         <v>717140.0</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C71" s="1">
         <v>10.0</v>
@@ -5239,7 +5248,7 @@
         <v>16</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>19</v>
@@ -5254,7 +5263,7 @@
         <v>21</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>19</v>
@@ -5274,7 +5283,7 @@
         <v>710493.0</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C72" s="1">
         <v>10.0</v>
@@ -5298,10 +5307,10 @@
         <v>121</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>45</v>
@@ -5318,7 +5327,7 @@
         <v>710200.0</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C73" s="1">
         <v>10.0</v>
@@ -5327,7 +5336,7 @@
         <v>16</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F73" s="1">
         <v>710493.0</v>
@@ -5342,10 +5351,10 @@
         <v>121</v>
       </c>
       <c r="J73" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="K73" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="L73" s="1" t="s">
         <v>45</v>
@@ -5362,7 +5371,7 @@
         <v>710600.0</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C74" s="1">
         <v>10.0</v>
@@ -5386,10 +5395,10 @@
         <v>121</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="L74" s="1" t="s">
         <v>45</v>
@@ -5406,7 +5415,7 @@
         <v>710770.0</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C75" s="1">
         <v>10.0</v>
@@ -5415,7 +5424,7 @@
         <v>16</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>19</v>
@@ -5430,10 +5439,10 @@
         <v>121</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="L75" s="1" t="s">
         <v>45</v>
@@ -5450,7 +5459,7 @@
         <v>710479.0</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C76" s="1">
         <v>10.0</v>
@@ -5474,10 +5483,10 @@
         <v>121</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L76" s="1" t="s">
         <v>45</v>
@@ -5494,7 +5503,7 @@
         <v>710480.0</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C77" s="1">
         <v>10.0</v>
@@ -5503,7 +5512,7 @@
         <v>16</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>19</v>
@@ -5518,10 +5527,10 @@
         <v>121</v>
       </c>
       <c r="J77" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="K77" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>45</v>
@@ -5538,7 +5547,7 @@
         <v>710481.0</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C78" s="1">
         <v>10.0</v>
@@ -5547,7 +5556,7 @@
         <v>16</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>19</v>
@@ -5562,10 +5571,10 @@
         <v>121</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L78" s="1" t="s">
         <v>45</v>
@@ -5582,7 +5591,7 @@
         <v>711280.0</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C79" s="1">
         <v>10.0</v>
@@ -5591,7 +5600,7 @@
         <v>16</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F79" s="1">
         <v>711225.0</v>
@@ -5603,10 +5612,10 @@
         <v>27</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="K79" s="1" t="s">
         <v>19</v>
@@ -5626,7 +5635,7 @@
         <v>710472.0</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C80" s="1">
         <v>10.0</v>
@@ -5635,7 +5644,7 @@
         <v>16</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>19</v>
@@ -5650,10 +5659,10 @@
         <v>121</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>45</v>
@@ -5670,7 +5679,7 @@
         <v>710773.0</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C81" s="1">
         <v>10.0</v>
@@ -5679,7 +5688,7 @@
         <v>16</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>19</v>
@@ -5694,10 +5703,10 @@
         <v>121</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>45</v>
@@ -5714,7 +5723,7 @@
         <v>710450.0</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C82" s="1">
         <v>10.0</v>
@@ -5738,10 +5747,10 @@
         <v>121</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L82" s="1" t="s">
         <v>45</v>
@@ -5758,7 +5767,7 @@
         <v>710451.0</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C83" s="1">
         <v>10.0</v>
@@ -5782,10 +5791,10 @@
         <v>121</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L83" s="1" t="s">
         <v>45</v>
@@ -5802,7 +5811,7 @@
         <v>710407.0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C84" s="1">
         <v>10.0</v>
@@ -5826,10 +5835,10 @@
         <v>121</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L84" s="1" t="s">
         <v>45</v>
@@ -5846,7 +5855,7 @@
         <v>710120.0</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C85" s="1">
         <v>10.0</v>
@@ -5870,10 +5879,10 @@
         <v>121</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>45</v>
@@ -5890,7 +5899,7 @@
         <v>711225.0</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C86" s="1">
         <v>10.0</v>
@@ -5911,10 +5920,10 @@
         <v>27</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K86" s="1" t="s">
         <v>19</v>
@@ -5934,7 +5943,7 @@
         <v>711282.0</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C87" s="1">
         <v>5.0</v>
@@ -5943,7 +5952,7 @@
         <v>82</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F87" s="1">
         <v>711225.0</v>
@@ -5955,10 +5964,10 @@
         <v>27</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="K87" s="1" t="s">
         <v>19</v>
@@ -5978,7 +5987,7 @@
         <v>711265.0</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C88" s="1">
         <v>10.0</v>
@@ -5987,7 +5996,7 @@
         <v>16</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F88" s="1">
         <v>711225.0</v>
@@ -5999,13 +6008,13 @@
         <v>27</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="L88" s="1" t="s">
         <v>50</v>
@@ -6022,7 +6031,7 @@
         <v>713780.0</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C89" s="1">
         <v>10.0</v>
@@ -6031,7 +6040,7 @@
         <v>16</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F89" s="1">
         <v>713760.0</v>
@@ -6043,13 +6052,13 @@
         <v>27</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="L89" s="1" t="s">
         <v>31</v>
@@ -6066,7 +6075,7 @@
         <v>713742.0</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C90" s="1">
         <v>10.0</v>
@@ -6075,7 +6084,7 @@
         <v>16</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="F90" s="1">
         <v>713760.0</v>
@@ -6090,10 +6099,10 @@
         <v>28</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L90" s="1" t="s">
         <v>50</v>
@@ -6110,7 +6119,7 @@
         <v>713735.0</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C91" s="1">
         <v>10.0</v>
@@ -6119,7 +6128,7 @@
         <v>16</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F91" s="1">
         <v>713760.0</v>
@@ -6134,10 +6143,10 @@
         <v>28</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>31</v>
@@ -6154,7 +6163,7 @@
         <v>713784.0</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C92" s="1">
         <v>10.0</v>
@@ -6178,10 +6187,10 @@
         <v>28</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>50</v>
@@ -6198,7 +6207,7 @@
         <v>711249.0</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C93" s="1">
         <v>10.0</v>
@@ -6207,7 +6216,7 @@
         <v>16</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F93" s="1">
         <v>711225.0</v>
@@ -6219,10 +6228,10 @@
         <v>27</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>19</v>
@@ -6239,16 +6248,16 @@
     </row>
     <row r="94">
       <c r="A94" s="2">
-        <v>711226.0</v>
+        <v>711228.0</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C94" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>303</v>
@@ -6263,7 +6272,7 @@
         <v>27</v>
       </c>
       <c r="I94" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J94" s="1" t="s">
         <v>304</v>
@@ -6283,10 +6292,10 @@
     </row>
     <row r="95">
       <c r="A95" s="2">
-        <v>713760.0</v>
+        <v>711226.0</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C95" s="1">
         <v>10.0</v>
@@ -6295,10 +6304,10 @@
         <v>16</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F95" s="1" t="s">
-        <v>19</v>
+        <v>307</v>
+      </c>
+      <c r="F95" s="1">
+        <v>711225.0</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>19</v>
@@ -6307,16 +6316,16 @@
         <v>27</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>307</v>
+        <v>19</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>27</v>
@@ -6327,10 +6336,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2">
-        <v>713725.0</v>
+        <v>713760.0</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C96" s="1">
         <v>10.0</v>
@@ -6339,10 +6348,10 @@
         <v>16</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="F96" s="1">
-        <v>713760.0</v>
+        <v>19</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>19</v>
@@ -6351,16 +6360,16 @@
         <v>27</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="M96" s="1" t="s">
         <v>27</v>
@@ -6371,19 +6380,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2">
-        <v>713727.0</v>
+        <v>713725.0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C97" s="1">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F97" s="1">
         <v>713760.0</v>
@@ -6398,10 +6407,10 @@
         <v>21</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>19</v>
+        <v>314</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>31</v>
@@ -6415,37 +6424,37 @@
     </row>
     <row r="98">
       <c r="A98" s="2">
-        <v>713757.0</v>
+        <v>713727.0</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C98" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>315</v>
+        <v>288</v>
+      </c>
+      <c r="F98" s="1">
+        <v>713760.0</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>316</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>317</v>
+        <v>19</v>
       </c>
       <c r="L98" s="1" t="s">
         <v>31</v>
@@ -6459,31 +6468,31 @@
     </row>
     <row r="99">
       <c r="A99" s="2">
-        <v>713788.0</v>
+        <v>713757.0</v>
       </c>
       <c r="B99" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="C99" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E99" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="C99" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E99" s="1" t="s">
+      <c r="F99" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" s="1">
-        <v>797081.0</v>
+      <c r="G99" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="H99" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>320</v>
@@ -6503,7 +6512,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2">
-        <v>713766.0</v>
+        <v>713788.0</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>322</v>
@@ -6518,25 +6527,25 @@
         <v>323</v>
       </c>
       <c r="F100" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J100" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="G100" s="1">
-        <v>797100.0</v>
-      </c>
-      <c r="H100" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="J100" s="1" t="s">
+      <c r="K100" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K100" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="L100" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>27</v>
@@ -6547,37 +6556,37 @@
     </row>
     <row r="101">
       <c r="A101" s="2">
-        <v>713767.0</v>
+        <v>713766.0</v>
       </c>
       <c r="B101" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="C101" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C101" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>323</v>
-      </c>
       <c r="F101" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G101" s="1">
         <v>797100.0</v>
       </c>
       <c r="H101" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>28</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K101" s="1" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L101" s="1" t="s">
         <v>50</v>
@@ -6591,10 +6600,10 @@
     </row>
     <row r="102">
       <c r="A102" s="2">
-        <v>713776.0</v>
+        <v>713767.0</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C102" s="1">
         <v>10.0</v>
@@ -6603,13 +6612,13 @@
         <v>16</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G102" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
+      </c>
+      <c r="G102" s="1">
+        <v>797100.0</v>
       </c>
       <c r="H102" s="1" t="s">
         <v>20</v>
@@ -6618,13 +6627,13 @@
         <v>28</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K102" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>27</v>
@@ -6635,25 +6644,25 @@
     </row>
     <row r="103">
       <c r="A103" s="2">
-        <v>713764.0</v>
+        <v>713776.0</v>
       </c>
       <c r="B103" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="C103" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="F103" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C103" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E103" s="1" t="s">
+      <c r="G103" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="F103" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="G103" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="H103" s="1" t="s">
         <v>20</v>
@@ -6662,13 +6671,13 @@
         <v>28</v>
       </c>
       <c r="J103" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K103" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="K103" s="1" t="s">
-        <v>339</v>
-      </c>
       <c r="L103" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M103" s="1" t="s">
         <v>27</v>
@@ -6679,25 +6688,25 @@
     </row>
     <row r="104">
       <c r="A104" s="2">
-        <v>713771.0</v>
+        <v>713764.0</v>
       </c>
       <c r="B104" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="C104" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E104" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="C104" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="F104" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="G104" s="1">
-        <v>797251.0</v>
+      <c r="G104" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="H104" s="1" t="s">
         <v>20</v>
@@ -6712,7 +6721,7 @@
         <v>343</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M104" s="1" t="s">
         <v>27</v>
@@ -6723,7 +6732,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2">
-        <v>713733.0</v>
+        <v>713771.0</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>344</v>
@@ -6738,25 +6747,25 @@
         <v>345</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G105" s="1">
-        <v>713760.0</v>
+        <v>335</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I105" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J105" s="1" t="s">
         <v>346</v>
       </c>
       <c r="K105" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L105" s="1">
-        <v>9.0</v>
+        <v>347</v>
+      </c>
+      <c r="L105" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>27</v>
@@ -6767,10 +6776,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2">
-        <v>716607.0</v>
+        <v>713733.0</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C106" s="1">
         <v>10.0</v>
@@ -6779,28 +6788,28 @@
         <v>16</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>19</v>
+        <v>349</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G106" s="1" t="s">
-        <v>19</v>
+      <c r="G106" s="1">
+        <v>713760.0</v>
       </c>
       <c r="H106" s="1" t="s">
         <v>27</v>
       </c>
       <c r="I106" s="1" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K106" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
+      </c>
+      <c r="L106" s="1">
+        <v>9.0</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>27</v>
@@ -6811,10 +6820,10 @@
     </row>
     <row r="107">
       <c r="A107" s="2">
-        <v>716604.0</v>
+        <v>716607.0</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C107" s="1">
         <v>10.0</v>
@@ -6835,16 +6844,16 @@
         <v>27</v>
       </c>
       <c r="I107" s="1" t="s">
-        <v>286</v>
+        <v>28</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>27</v>
@@ -6855,10 +6864,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2">
-        <v>716208.0</v>
+        <v>716604.0</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C108" s="1">
         <v>10.0</v>
@@ -6879,16 +6888,16 @@
         <v>27</v>
       </c>
       <c r="I108" s="1" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="J108" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="K108" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="K108" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="L108" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M108" s="1" t="s">
         <v>27</v>
@@ -6899,10 +6908,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2">
-        <v>716609.0</v>
+        <v>716208.0</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C109" s="1">
         <v>10.0</v>
@@ -6911,7 +6920,7 @@
         <v>16</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>19</v>
@@ -6923,7 +6932,7 @@
         <v>27</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>128</v>
+        <v>21</v>
       </c>
       <c r="J109" s="1" t="s">
         <v>357</v>
@@ -6943,7 +6952,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2">
-        <v>716608.0</v>
+        <v>716609.0</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>359</v>
@@ -6955,7 +6964,7 @@
         <v>16</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>19</v>
@@ -6967,16 +6976,16 @@
         <v>27</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="L110" s="1">
-        <v>12.0</v>
+        <v>362</v>
+      </c>
+      <c r="L110" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>27</v>
@@ -6987,19 +6996,19 @@
     </row>
     <row r="111">
       <c r="A111" s="2">
-        <v>716605.0</v>
+        <v>716608.0</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C111" s="1">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>19</v>
@@ -7011,16 +7020,16 @@
         <v>27</v>
       </c>
       <c r="I111" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J111" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="K111" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="K111" s="1" t="s">
-        <v>358</v>
-      </c>
       <c r="L111" s="1">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>27</v>
@@ -7031,19 +7040,19 @@
     </row>
     <row r="112">
       <c r="A112" s="2">
-        <v>716602.0</v>
+        <v>716605.0</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C112" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>19</v>
@@ -7055,16 +7064,16 @@
         <v>27</v>
       </c>
       <c r="I112" s="1" t="s">
-        <v>286</v>
+        <v>139</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="L112" s="1" t="s">
-        <v>45</v>
+        <v>362</v>
+      </c>
+      <c r="L112" s="1">
+        <v>10.0</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>27</v>
@@ -7075,10 +7084,10 @@
     </row>
     <row r="113">
       <c r="A113" s="2">
-        <v>716611.0</v>
+        <v>716602.0</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C113" s="1">
         <v>10.0</v>
@@ -7087,7 +7096,7 @@
         <v>16</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>19</v>
@@ -7099,16 +7108,16 @@
         <v>27</v>
       </c>
       <c r="I113" s="1" t="s">
-        <v>56</v>
+        <v>289</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>164</v>
+        <v>45</v>
       </c>
       <c r="M113" s="1" t="s">
         <v>27</v>
@@ -7119,10 +7128,10 @@
     </row>
     <row r="114">
       <c r="A114" s="2">
-        <v>716612.0</v>
+        <v>716611.0</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C114" s="1">
         <v>10.0</v>
@@ -7131,7 +7140,7 @@
         <v>16</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>19</v>
@@ -7146,13 +7155,13 @@
         <v>56</v>
       </c>
       <c r="J114" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="L114" s="3">
-        <v>46307.0</v>
+        <v>371</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>164</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>27</v>
@@ -7163,10 +7172,10 @@
     </row>
     <row r="115">
       <c r="A115" s="2">
-        <v>716600.0</v>
+        <v>716612.0</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C115" s="1">
         <v>10.0</v>
@@ -7175,7 +7184,7 @@
         <v>16</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>19</v>
@@ -7187,16 +7196,16 @@
         <v>27</v>
       </c>
       <c r="I115" s="1" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="J115" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="K115" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="K115" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>45</v>
+      <c r="L115" s="3">
+        <v>46307.0</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>27</v>
@@ -7207,10 +7216,10 @@
     </row>
     <row r="116">
       <c r="A116" s="2">
-        <v>716601.0</v>
+        <v>716600.0</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C116" s="1">
         <v>10.0</v>
@@ -7219,7 +7228,7 @@
         <v>16</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
@@ -7234,10 +7243,10 @@
         <v>161</v>
       </c>
       <c r="J116" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>45</v>
@@ -7251,10 +7260,10 @@
     </row>
     <row r="117">
       <c r="A117" s="2">
-        <v>713785.0</v>
+        <v>716601.0</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C117" s="1">
         <v>10.0</v>
@@ -7263,28 +7272,28 @@
         <v>16</v>
       </c>
       <c r="E117" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="K117" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F117" s="1">
-        <v>713760.0</v>
-      </c>
-      <c r="G117" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H117" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I117" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="J117" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="K117" s="1" t="s">
-        <v>378</v>
-      </c>
       <c r="L117" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>27</v>
@@ -7295,7 +7304,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2">
-        <v>713737.0</v>
+        <v>713785.0</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>379</v>
@@ -7309,26 +7318,26 @@
       <c r="E118" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="F118" s="1" t="s">
+      <c r="F118" s="1">
+        <v>713760.0</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J118" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="G118" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I118" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J118" s="1" t="s">
+      <c r="K118" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="K118" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="L118" s="1">
-        <v>12.0</v>
+      <c r="L118" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>27</v>
@@ -7339,7 +7348,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2">
-        <v>713736.0</v>
+        <v>713737.0</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>383</v>
@@ -7353,8 +7362,8 @@
       <c r="E119" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="F119" s="1">
-        <v>713785.0</v>
+      <c r="F119" s="1" t="s">
+        <v>385</v>
       </c>
       <c r="G119" s="1" t="s">
         <v>19</v>
@@ -7363,16 +7372,16 @@
         <v>20</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>31</v>
+        <v>132</v>
+      </c>
+      <c r="L119" s="1">
+        <v>12.0</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>27</v>
@@ -7382,41 +7391,41 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="s">
+      <c r="A120" s="2">
+        <v>713736.0</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C120" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>19</v>
+      <c r="F120" s="1">
+        <v>713785.0</v>
       </c>
       <c r="G120" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I120" s="1" t="s">
-        <v>21</v>
+        <v>289</v>
       </c>
       <c r="J120" s="1" t="s">
         <v>389</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L120" s="1">
-        <v>12.0</v>
+        <v>390</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>27</v>
@@ -7427,10 +7436,10 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C121" s="1">
         <v>10.0</v>
@@ -7439,7 +7448,7 @@
         <v>16</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>19</v>
@@ -7451,10 +7460,10 @@
         <v>27</v>
       </c>
       <c r="I121" s="1" t="s">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="J121" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K121" s="1" t="s">
         <v>19</v>
@@ -7471,10 +7480,10 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C122" s="1">
         <v>10.0</v>
@@ -7483,7 +7492,7 @@
         <v>16</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>19</v>
@@ -7495,10 +7504,10 @@
         <v>27</v>
       </c>
       <c r="I122" s="1" t="s">
-        <v>28</v>
+        <v>289</v>
       </c>
       <c r="J122" s="1" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K122" s="1" t="s">
         <v>19</v>
@@ -7515,10 +7524,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>347</v>
+        <v>398</v>
       </c>
       <c r="C123" s="1">
         <v>10.0</v>
@@ -7527,7 +7536,7 @@
         <v>16</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>19</v>
+        <v>360</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>19</v>
@@ -7542,10 +7551,10 @@
         <v>28</v>
       </c>
       <c r="J123" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>349</v>
+        <v>19</v>
       </c>
       <c r="L123" s="1">
         <v>12.0</v>
@@ -7559,10 +7568,10 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C124" s="1">
         <v>10.0</v>
@@ -7583,71 +7592,71 @@
         <v>27</v>
       </c>
       <c r="I124" s="1" t="s">
-        <v>286</v>
+        <v>28</v>
       </c>
       <c r="J124" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K124" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="L124" s="4">
+        <v>353</v>
+      </c>
+      <c r="L124" s="1">
+        <v>12.0</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C125" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="K125" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="L125" s="4">
         <v>41162.0</v>
       </c>
-      <c r="M124" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N124" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2">
+      <c r="M125" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N125" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2">
         <v>716150.0</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>400</v>
-      </c>
-      <c r="C125" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H125" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I125" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J125" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="K125" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="L125" s="1">
-        <v>12.0</v>
-      </c>
-      <c r="M125" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N125" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>404</v>
@@ -7677,7 +7686,7 @@
         <v>405</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>19</v>
+        <v>406</v>
       </c>
       <c r="L126" s="1">
         <v>12.0</v>
@@ -7691,10 +7700,10 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C127" s="1">
         <v>10.0</v>
@@ -7715,16 +7724,16 @@
         <v>27</v>
       </c>
       <c r="I127" s="1" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="J127" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="K127" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="L127" s="1" t="s">
-        <v>45</v>
+        <v>19</v>
+      </c>
+      <c r="L127" s="1">
+        <v>12.0</v>
       </c>
       <c r="M127" s="1" t="s">
         <v>27</v>
@@ -7759,16 +7768,16 @@
         <v>27</v>
       </c>
       <c r="I128" s="1" t="s">
-        <v>161</v>
+        <v>56</v>
       </c>
       <c r="J128" s="1" t="s">
         <v>412</v>
       </c>
       <c r="K128" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="L128" s="4">
-        <v>41162.0</v>
+        <v>413</v>
+      </c>
+      <c r="L128" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>27</v>
@@ -7779,40 +7788,40 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C129" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F129" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J129" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="K129" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B129" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C129" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H129" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I129" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="J129" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="K129" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="L129" s="3">
-        <v>46307.0</v>
+      <c r="L129" s="4">
+        <v>41162.0</v>
       </c>
       <c r="M129" s="1" t="s">
         <v>27</v>
@@ -7823,10 +7832,10 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C130" s="1">
         <v>10.0</v>
@@ -7835,7 +7844,7 @@
         <v>16</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>356</v>
+        <v>19</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>19</v>
@@ -7847,16 +7856,16 @@
         <v>27</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L130" s="1">
-        <v>12.0</v>
+        <v>358</v>
+      </c>
+      <c r="L130" s="3">
+        <v>46307.0</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>27</v>
@@ -7867,10 +7876,10 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C131" s="1">
         <v>10.0</v>
@@ -7879,7 +7888,7 @@
         <v>16</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>19</v>
@@ -7891,10 +7900,10 @@
         <v>27</v>
       </c>
       <c r="I131" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K131" s="1" t="s">
         <v>19</v>
@@ -7911,10 +7920,10 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C132" s="1">
         <v>10.0</v>
@@ -7923,7 +7932,7 @@
         <v>16</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>19</v>
@@ -7935,10 +7944,10 @@
         <v>27</v>
       </c>
       <c r="I132" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="K132" s="1" t="s">
         <v>19</v>
@@ -7955,10 +7964,10 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C133" s="1">
         <v>10.0</v>
@@ -7967,7 +7976,7 @@
         <v>16</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>19</v>
@@ -7979,10 +7988,10 @@
         <v>27</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K133" s="1" t="s">
         <v>19</v>
@@ -7999,19 +8008,19 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C134" s="1">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>19</v>
@@ -8023,13 +8032,13 @@
         <v>27</v>
       </c>
       <c r="I134" s="1" t="s">
-        <v>139</v>
+        <v>161</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>358</v>
+        <v>19</v>
       </c>
       <c r="L134" s="1">
         <v>12.0</v>
@@ -8043,10 +8052,10 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>361</v>
+        <v>433</v>
       </c>
       <c r="C135" s="1">
         <v>5.0</v>
@@ -8055,7 +8064,7 @@
         <v>82</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>19</v>
@@ -8070,10 +8079,10 @@
         <v>139</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="K135" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L135" s="1">
         <v>12.0</v>
@@ -8087,19 +8096,19 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C136" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>19</v>
@@ -8111,16 +8120,16 @@
         <v>27</v>
       </c>
       <c r="I136" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="K136" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>31</v>
+        <v>362</v>
+      </c>
+      <c r="L136" s="1">
+        <v>12.0</v>
       </c>
       <c r="M136" s="1" t="s">
         <v>27</v>
@@ -8131,7 +8140,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>363</v>
@@ -8143,7 +8152,7 @@
         <v>16</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>19</v>
@@ -8155,74 +8164,74 @@
         <v>27</v>
       </c>
       <c r="I137" s="1" t="s">
-        <v>286</v>
+        <v>134</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="K137" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="L137" s="1">
+        <v>362</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N137" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C138" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="L138" s="1">
         <v>12.0</v>
       </c>
-      <c r="M137" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N137" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2">
-        <v>715179.0</v>
-      </c>
-      <c r="B138" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="C138" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H138" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I138" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="J138" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="K138" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L138" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="M138" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N138" s="1" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2">
-        <v>715178.0</v>
+        <v>715179.0</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C139" s="1">
         <v>10.0</v>
@@ -8246,7 +8255,7 @@
         <v>121</v>
       </c>
       <c r="J139" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="K139" s="1" t="s">
         <v>23</v>
@@ -8263,10 +8272,10 @@
     </row>
     <row r="140">
       <c r="A140" s="2">
-        <v>715118.0</v>
+        <v>715178.0</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C140" s="1">
         <v>10.0</v>
@@ -8275,10 +8284,10 @@
         <v>16</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="F140" s="1">
-        <v>715117.0</v>
+        <v>19</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G140" s="1" t="s">
         <v>19</v>
@@ -8290,7 +8299,7 @@
         <v>121</v>
       </c>
       <c r="J140" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K140" s="1" t="s">
         <v>23</v>
@@ -8302,27 +8311,27 @@
         <v>20</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>444</v>
+        <v>32</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2">
-        <v>715190.0</v>
+        <v>715118.0</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>445</v>
       </c>
       <c r="C141" s="1">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="D141" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E141" s="1" t="s">
         <v>446</v>
       </c>
-      <c r="E141" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F141" s="1" t="s">
-        <v>19</v>
+      <c r="F141" s="1">
+        <v>715117.0</v>
       </c>
       <c r="G141" s="1" t="s">
         <v>19</v>
@@ -8331,7 +8340,7 @@
         <v>27</v>
       </c>
       <c r="I141" s="1" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="J141" s="1" t="s">
         <v>447</v>
@@ -8340,33 +8349,33 @@
         <v>23</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N141" s="1" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2">
-        <v>715170.0</v>
+        <v>715190.0</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C142" s="1">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>16</v>
+        <v>450</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G142" s="1" t="s">
         <v>19</v>
@@ -8378,27 +8387,27 @@
         <v>21</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="K142" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N142" s="1" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2">
-        <v>715236.0</v>
+        <v>715170.0</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C143" s="1">
         <v>10.0</v>
@@ -8407,10 +8416,10 @@
         <v>16</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G143" s="1" t="s">
         <v>19</v>
@@ -8422,7 +8431,7 @@
         <v>21</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K143" s="1" t="s">
         <v>23</v>
@@ -8434,15 +8443,15 @@
         <v>20</v>
       </c>
       <c r="N143" s="1" t="s">
-        <v>24</v>
+        <v>454</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2">
-        <v>715117.0</v>
+        <v>715236.0</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="C144" s="1">
         <v>10.0</v>
@@ -8466,7 +8475,7 @@
         <v>21</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K144" s="1" t="s">
         <v>23</v>
@@ -8478,15 +8487,15 @@
         <v>20</v>
       </c>
       <c r="N144" s="1" t="s">
-        <v>444</v>
+        <v>24</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2">
-        <v>715195.0</v>
+        <v>715117.0</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="C145" s="1">
         <v>10.0</v>
@@ -8510,27 +8519,27 @@
         <v>21</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="K145" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L145" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M145" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N145" s="1" t="s">
-        <v>32</v>
+        <v>448</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2">
-        <v>715194.0</v>
+        <v>715195.0</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C146" s="1">
         <v>10.0</v>
@@ -8554,10 +8563,10 @@
         <v>21</v>
       </c>
       <c r="J146" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K146" s="1" t="s">
-        <v>458</v>
+        <v>23</v>
       </c>
       <c r="L146" s="1" t="s">
         <v>50</v>
@@ -8571,10 +8580,10 @@
     </row>
     <row r="147">
       <c r="A147" s="2">
-        <v>715200.0</v>
+        <v>715194.0</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C147" s="1">
         <v>10.0</v>
@@ -8583,10 +8592,10 @@
         <v>16</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="F147" s="1">
-        <v>715194.0</v>
+        <v>19</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>19</v>
@@ -8601,10 +8610,10 @@
         <v>461</v>
       </c>
       <c r="K147" s="1" t="s">
-        <v>23</v>
+        <v>462</v>
       </c>
       <c r="L147" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M147" s="1" t="s">
         <v>20</v>
@@ -8615,10 +8624,10 @@
     </row>
     <row r="148">
       <c r="A148" s="2">
-        <v>715101.0</v>
+        <v>715200.0</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C148" s="1">
         <v>10.0</v>
@@ -8627,10 +8636,10 @@
         <v>16</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F148" s="1" t="s">
-        <v>19</v>
+        <v>464</v>
+      </c>
+      <c r="F148" s="1">
+        <v>715194.0</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>19</v>
@@ -8642,7 +8651,7 @@
         <v>21</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="K148" s="1" t="s">
         <v>23</v>
@@ -8654,15 +8663,15 @@
         <v>20</v>
       </c>
       <c r="N148" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2">
-        <v>715103.0</v>
+        <v>715101.0</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C149" s="1">
         <v>10.0</v>
@@ -8686,7 +8695,7 @@
         <v>21</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="K149" s="1" t="s">
         <v>23</v>
@@ -8703,10 +8712,10 @@
     </row>
     <row r="150">
       <c r="A150" s="2">
-        <v>715104.0</v>
+        <v>715103.0</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C150" s="1">
         <v>10.0</v>
@@ -8730,27 +8739,27 @@
         <v>21</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="K150" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L150" s="1" t="s">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="M150" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N150" s="1" t="s">
-        <v>468</v>
+        <v>24</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2">
-        <v>715106.0</v>
+        <v>715104.0</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C151" s="1">
         <v>10.0</v>
@@ -8762,7 +8771,7 @@
         <v>19</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>470</v>
+        <v>19</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>19</v>
@@ -8780,21 +8789,21 @@
         <v>23</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="M151" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2">
-        <v>715188.0</v>
+        <v>715106.0</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C152" s="1">
         <v>10.0</v>
@@ -8803,10 +8812,10 @@
         <v>16</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>473</v>
+        <v>19</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>19</v>
+        <v>474</v>
       </c>
       <c r="G152" s="1" t="s">
         <v>19</v>
@@ -8818,7 +8827,7 @@
         <v>21</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="K152" s="1" t="s">
         <v>23</v>
@@ -8830,12 +8839,12 @@
         <v>20</v>
       </c>
       <c r="N152" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2">
-        <v>715189.0</v>
+        <v>715188.0</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>476</v>
@@ -8847,7 +8856,7 @@
         <v>16</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>19</v>
@@ -8862,7 +8871,7 @@
         <v>21</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="K153" s="1" t="s">
         <v>23</v>
@@ -8874,15 +8883,15 @@
         <v>20</v>
       </c>
       <c r="N153" s="1" t="s">
-        <v>444</v>
+        <v>479</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2">
-        <v>724000.0</v>
+        <v>715189.0</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C154" s="1">
         <v>10.0</v>
@@ -8891,7 +8900,7 @@
         <v>16</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>19</v>
+        <v>477</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>19</v>
@@ -8903,30 +8912,30 @@
         <v>27</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="K154" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M154" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N154" s="1" t="s">
-        <v>19</v>
+        <v>448</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2">
-        <v>715800.0</v>
+        <v>724000.0</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C155" s="1">
         <v>10.0</v>
@@ -8935,7 +8944,7 @@
         <v>16</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>481</v>
+        <v>19</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>19</v>
@@ -8944,19 +8953,19 @@
         <v>19</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="K155" s="1" t="s">
-        <v>483</v>
+        <v>19</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>27</v>
@@ -8967,7 +8976,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2">
-        <v>724220.0</v>
+        <v>715800.0</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>484</v>
@@ -8997,10 +9006,10 @@
         <v>486</v>
       </c>
       <c r="K156" s="1" t="s">
-        <v>19</v>
+        <v>487</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M156" s="1" t="s">
         <v>27</v>
@@ -9011,10 +9020,10 @@
     </row>
     <row r="157">
       <c r="A157" s="2">
-        <v>753331.0</v>
+        <v>724220.0</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C157" s="1">
         <v>10.0</v>
@@ -9023,7 +9032,7 @@
         <v>16</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>19</v>
+        <v>489</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>19</v>
@@ -9032,19 +9041,19 @@
         <v>19</v>
       </c>
       <c r="H157" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K157" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="L157" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M157" s="1" t="s">
         <v>27</v>
@@ -9055,10 +9064,10 @@
     </row>
     <row r="158">
       <c r="A158" s="2">
-        <v>753333.0</v>
+        <v>753331.0</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C158" s="1">
         <v>10.0</v>
@@ -9067,28 +9076,28 @@
         <v>16</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="F158" s="1">
-        <v>753331.0</v>
+        <v>19</v>
+      </c>
+      <c r="F158" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G158" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="K158" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L158" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M158" s="1" t="s">
         <v>27</v>
@@ -9099,10 +9108,10 @@
     </row>
     <row r="159">
       <c r="A159" s="2">
-        <v>724200.0</v>
+        <v>753333.0</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C159" s="1">
         <v>10.0</v>
@@ -9111,28 +9120,28 @@
         <v>16</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F159" s="1" t="s">
-        <v>19</v>
+        <v>494</v>
+      </c>
+      <c r="F159" s="1">
+        <v>753331.0</v>
       </c>
       <c r="G159" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H159" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="K159" s="1" t="s">
-        <v>494</v>
+        <v>23</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M159" s="1" t="s">
         <v>27</v>
@@ -9143,10 +9152,10 @@
     </row>
     <row r="160">
       <c r="A160" s="2">
-        <v>724600.0</v>
+        <v>724200.0</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C160" s="1">
         <v>10.0</v>
@@ -9170,10 +9179,10 @@
         <v>121</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="K160" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="L160" s="1" t="s">
         <v>45</v>
@@ -9187,10 +9196,10 @@
     </row>
     <row r="161">
       <c r="A161" s="2">
-        <v>715237.0</v>
+        <v>724600.0</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C161" s="1">
         <v>10.0</v>
@@ -9211,30 +9220,30 @@
         <v>27</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="K161" s="1" t="s">
-        <v>23</v>
+        <v>501</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="M161" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N161" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2">
-        <v>715238.0</v>
+        <v>715237.0</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C162" s="1">
         <v>10.0</v>
@@ -9243,10 +9252,10 @@
         <v>16</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="F162" s="1">
-        <v>715237.0</v>
+        <v>19</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G162" s="1" t="s">
         <v>19</v>
@@ -9258,13 +9267,13 @@
         <v>21</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="L162" s="1">
-        <v>12.0</v>
+        <v>23</v>
+      </c>
+      <c r="L162" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="M162" s="1" t="s">
         <v>20</v>
@@ -9275,10 +9284,10 @@
     </row>
     <row r="163">
       <c r="A163" s="2">
-        <v>715112.0</v>
+        <v>715238.0</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C163" s="1">
         <v>10.0</v>
@@ -9287,10 +9296,10 @@
         <v>16</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>19</v>
+        <v>502</v>
+      </c>
+      <c r="F163" s="1">
+        <v>715237.0</v>
       </c>
       <c r="G163" s="1" t="s">
         <v>19</v>
@@ -9302,27 +9311,27 @@
         <v>21</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="K163" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="L163" s="1" t="s">
-        <v>31</v>
+        <v>506</v>
+      </c>
+      <c r="L163" s="1">
+        <v>12.0</v>
       </c>
       <c r="M163" s="1" t="s">
         <v>20</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2">
-        <v>715173.0</v>
+        <v>715112.0</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C164" s="1">
         <v>10.0</v>
@@ -9346,13 +9355,13 @@
         <v>21</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K164" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="M164" s="1" t="s">
         <v>20</v>
@@ -9363,10 +9372,10 @@
     </row>
     <row r="165">
       <c r="A165" s="2">
-        <v>715193.0</v>
+        <v>715173.0</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C165" s="1">
         <v>10.0</v>
@@ -9390,7 +9399,7 @@
         <v>21</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="K165" s="1" t="s">
         <v>23</v>
@@ -9407,10 +9416,10 @@
     </row>
     <row r="166">
       <c r="A166" s="2">
-        <v>715171.0</v>
+        <v>715193.0</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C166" s="1">
         <v>10.0</v>
@@ -9434,7 +9443,7 @@
         <v>21</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="K166" s="1" t="s">
         <v>23</v>
@@ -9451,10 +9460,10 @@
     </row>
     <row r="167">
       <c r="A167" s="2">
-        <v>724441.0</v>
+        <v>715171.0</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C167" s="1">
         <v>10.0</v>
@@ -9463,39 +9472,39 @@
         <v>16</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="F167" s="1">
-        <v>724000.0</v>
+        <v>19</v>
+      </c>
+      <c r="F167" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G167" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H167" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I167" s="1" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>514</v>
+        <v>23</v>
       </c>
       <c r="L167" s="1" t="s">
         <v>50</v>
       </c>
       <c r="M167" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2">
-        <v>724443.0</v>
+        <v>724441.0</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>515</v>
@@ -9509,8 +9518,8 @@
       <c r="E168" s="1" t="s">
         <v>516</v>
       </c>
-      <c r="F168" s="1" t="s">
-        <v>19</v>
+      <c r="F168" s="1">
+        <v>724000.0</v>
       </c>
       <c r="G168" s="1" t="s">
         <v>19</v>
@@ -9522,10 +9531,10 @@
         <v>121</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="K168" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L168" s="1" t="s">
         <v>50</v>
@@ -9539,10 +9548,10 @@
     </row>
     <row r="169">
       <c r="A169" s="2">
-        <v>724444.0</v>
+        <v>724443.0</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C169" s="1">
         <v>10.0</v>
@@ -9551,7 +9560,7 @@
         <v>16</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>19</v>
@@ -9566,13 +9575,13 @@
         <v>121</v>
       </c>
       <c r="J169" s="1" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="K169" s="1" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M169" s="1" t="s">
         <v>27</v>
@@ -9583,10 +9592,10 @@
     </row>
     <row r="170">
       <c r="A170" s="2">
-        <v>724300.0</v>
+        <v>724444.0</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C170" s="1">
         <v>10.0</v>
@@ -9595,7 +9604,7 @@
         <v>16</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>19</v>
+        <v>522</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>19</v>
@@ -9604,19 +9613,19 @@
         <v>19</v>
       </c>
       <c r="H170" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>121</v>
       </c>
       <c r="J170" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K170" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M170" s="1" t="s">
         <v>27</v>
@@ -9627,10 +9636,10 @@
     </row>
     <row r="171">
       <c r="A171" s="2">
-        <v>724310.0</v>
+        <v>724300.0</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C171" s="1">
         <v>10.0</v>
@@ -9639,10 +9648,10 @@
         <v>16</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="F171" s="1">
-        <v>724300.0</v>
+        <v>19</v>
+      </c>
+      <c r="F171" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G171" s="1" t="s">
         <v>19</v>
@@ -9657,7 +9666,7 @@
         <v>524</v>
       </c>
       <c r="K171" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L171" s="1" t="s">
         <v>45</v>
@@ -9671,10 +9680,10 @@
     </row>
     <row r="172">
       <c r="A172" s="2">
-        <v>724311.0</v>
+        <v>724310.0</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C172" s="1">
         <v>10.0</v>
@@ -9683,16 +9692,16 @@
         <v>16</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="F172" s="1" t="s">
         <v>527</v>
       </c>
+      <c r="F172" s="1">
+        <v>724300.0</v>
+      </c>
       <c r="G172" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>121</v>
@@ -9701,10 +9710,10 @@
         <v>528</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="M172" s="1" t="s">
         <v>27</v>
@@ -9715,7 +9724,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2">
-        <v>765000.0</v>
+        <v>724311.0</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>529</v>
@@ -9727,28 +9736,28 @@
         <v>16</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>19</v>
+        <v>530</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>19</v>
+        <v>531</v>
       </c>
       <c r="G173" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H173" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>530</v>
+        <v>121</v>
       </c>
       <c r="J173" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="K173" s="1" t="s">
-        <v>23</v>
+        <v>525</v>
       </c>
       <c r="L173" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M173" s="1" t="s">
         <v>27</v>
@@ -9759,10 +9768,10 @@
     </row>
     <row r="174">
       <c r="A174" s="2">
-        <v>765020.0</v>
+        <v>765000.0</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C174" s="1">
         <v>10.0</v>
@@ -9771,10 +9780,10 @@
         <v>16</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="F174" s="1">
-        <v>765000.0</v>
+        <v>19</v>
+      </c>
+      <c r="F174" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G174" s="1" t="s">
         <v>19</v>
@@ -9783,13 +9792,13 @@
         <v>27</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="K174" s="1" t="s">
-        <v>535</v>
+        <v>23</v>
       </c>
       <c r="L174" s="1" t="s">
         <v>45</v>
@@ -9803,7 +9812,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2">
-        <v>765040.0</v>
+        <v>765020.0</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>536</v>
@@ -9818,7 +9827,7 @@
         <v>537</v>
       </c>
       <c r="F175" s="1">
-        <v>765020.0</v>
+        <v>765000.0</v>
       </c>
       <c r="G175" s="1" t="s">
         <v>19</v>
@@ -9827,13 +9836,13 @@
         <v>27</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J175" s="1" t="s">
         <v>538</v>
       </c>
       <c r="K175" s="1" t="s">
-        <v>23</v>
+        <v>539</v>
       </c>
       <c r="L175" s="1" t="s">
         <v>45</v>
@@ -9847,10 +9856,10 @@
     </row>
     <row r="176">
       <c r="A176" s="2">
-        <v>765060.0</v>
+        <v>765040.0</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C176" s="1">
         <v>10.0</v>
@@ -9859,28 +9868,28 @@
         <v>16</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="F176" s="1">
-        <v>765060.0</v>
+        <v>765020.0</v>
       </c>
       <c r="G176" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H176" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I176" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J176" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="K176" s="1" t="s">
-        <v>502</v>
+        <v>23</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M176" s="1" t="s">
         <v>27</v>
@@ -9891,10 +9900,10 @@
     </row>
     <row r="177">
       <c r="A177" s="2">
-        <v>765315.0</v>
+        <v>765060.0</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C177" s="1">
         <v>10.0</v>
@@ -9903,28 +9912,28 @@
         <v>16</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="F177" s="1">
-        <v>765310.0</v>
+        <v>765060.0</v>
       </c>
       <c r="G177" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H177" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I177" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J177" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="K177" s="1" t="s">
-        <v>23</v>
+        <v>506</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M177" s="1" t="s">
         <v>27</v>
@@ -9935,10 +9944,10 @@
     </row>
     <row r="178">
       <c r="A178" s="2">
-        <v>765320.0</v>
+        <v>765315.0</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C178" s="1">
         <v>10.0</v>
@@ -9947,28 +9956,28 @@
         <v>16</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="F178" s="1">
-        <v>765315.0</v>
+        <v>765310.0</v>
       </c>
       <c r="G178" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H178" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I178" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J178" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="K178" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M178" s="1" t="s">
         <v>27</v>
@@ -9979,10 +9988,10 @@
     </row>
     <row r="179">
       <c r="A179" s="2">
-        <v>765325.0</v>
+        <v>765320.0</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C179" s="1">
         <v>10.0</v>
@@ -9991,10 +10000,10 @@
         <v>16</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="F179" s="1">
-        <v>765320.0</v>
+        <v>765315.0</v>
       </c>
       <c r="G179" s="1" t="s">
         <v>19</v>
@@ -10003,10 +10012,10 @@
         <v>20</v>
       </c>
       <c r="I179" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J179" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="K179" s="1" t="s">
         <v>23</v>
@@ -10023,10 +10032,10 @@
     </row>
     <row r="180">
       <c r="A180" s="2">
-        <v>765300.0</v>
+        <v>765325.0</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C180" s="1">
         <v>10.0</v>
@@ -10035,28 +10044,28 @@
         <v>16</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F180" s="1" t="s">
-        <v>19</v>
+        <v>553</v>
+      </c>
+      <c r="F180" s="1">
+        <v>765320.0</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H180" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I180" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J180" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="K180" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M180" s="1" t="s">
         <v>27</v>
@@ -10067,10 +10076,10 @@
     </row>
     <row r="181">
       <c r="A181" s="2">
-        <v>765310.0</v>
+        <v>765300.0</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C181" s="1">
         <v>10.0</v>
@@ -10079,10 +10088,10 @@
         <v>16</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="F181" s="1">
-        <v>765310.0</v>
+        <v>19</v>
+      </c>
+      <c r="F181" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G181" s="1" t="s">
         <v>19</v>
@@ -10091,10 +10100,10 @@
         <v>27</v>
       </c>
       <c r="I181" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J181" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="K181" s="1" t="s">
         <v>23</v>
@@ -10111,10 +10120,10 @@
     </row>
     <row r="182">
       <c r="A182" s="2">
-        <v>765100.0</v>
+        <v>765310.0</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C182" s="1">
         <v>10.0</v>
@@ -10123,10 +10132,10 @@
         <v>16</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F182" s="1" t="s">
-        <v>19</v>
+        <v>558</v>
+      </c>
+      <c r="F182" s="1">
+        <v>765310.0</v>
       </c>
       <c r="G182" s="1" t="s">
         <v>19</v>
@@ -10135,10 +10144,10 @@
         <v>27</v>
       </c>
       <c r="I182" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J182" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K182" s="1" t="s">
         <v>23</v>
@@ -10155,10 +10164,10 @@
     </row>
     <row r="183">
       <c r="A183" s="2">
-        <v>765120.0</v>
+        <v>765100.0</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C183" s="1">
         <v>10.0</v>
@@ -10167,10 +10176,10 @@
         <v>16</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="F183" s="1">
-        <v>765100.0</v>
+        <v>19</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G183" s="1" t="s">
         <v>19</v>
@@ -10179,10 +10188,10 @@
         <v>27</v>
       </c>
       <c r="I183" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J183" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="K183" s="1" t="s">
         <v>23</v>
@@ -10199,10 +10208,10 @@
     </row>
     <row r="184">
       <c r="A184" s="2">
-        <v>765140.0</v>
+        <v>765120.0</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C184" s="1">
         <v>10.0</v>
@@ -10211,10 +10220,10 @@
         <v>16</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="F184" s="1">
-        <v>765120.0</v>
+        <v>765100.0</v>
       </c>
       <c r="G184" s="1" t="s">
         <v>19</v>
@@ -10223,10 +10232,10 @@
         <v>27</v>
       </c>
       <c r="I184" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J184" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="K184" s="1" t="s">
         <v>23</v>
@@ -10243,10 +10252,10 @@
     </row>
     <row r="185">
       <c r="A185" s="2">
-        <v>765162.0</v>
+        <v>765140.0</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C185" s="1">
         <v>10.0</v>
@@ -10255,28 +10264,28 @@
         <v>16</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="F185" s="1">
-        <v>765140.0</v>
+        <v>765120.0</v>
       </c>
       <c r="G185" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H185" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I185" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J185" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="K185" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M185" s="1" t="s">
         <v>27</v>
@@ -10287,10 +10296,10 @@
     </row>
     <row r="186">
       <c r="A186" s="2">
-        <v>765191.0</v>
+        <v>765162.0</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C186" s="1">
         <v>10.0</v>
@@ -10299,10 +10308,10 @@
         <v>16</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F186" s="1">
-        <v>765162.0</v>
+        <v>765140.0</v>
       </c>
       <c r="G186" s="1" t="s">
         <v>19</v>
@@ -10311,10 +10320,10 @@
         <v>20</v>
       </c>
       <c r="I186" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J186" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="K186" s="1" t="s">
         <v>23</v>
@@ -10331,10 +10340,10 @@
     </row>
     <row r="187">
       <c r="A187" s="2">
-        <v>765080.0</v>
+        <v>765191.0</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C187" s="1">
         <v>10.0</v>
@@ -10343,10 +10352,10 @@
         <v>16</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F187" s="1">
-        <v>765060.0</v>
+        <v>765162.0</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>19</v>
@@ -10355,16 +10364,16 @@
         <v>20</v>
       </c>
       <c r="I187" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J187" s="1" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="K187" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="M187" s="1" t="s">
         <v>27</v>
@@ -10375,10 +10384,10 @@
     </row>
     <row r="188">
       <c r="A188" s="2">
-        <v>765400.0</v>
+        <v>765080.0</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C188" s="1">
         <v>10.0</v>
@@ -10387,28 +10396,28 @@
         <v>16</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>19</v>
+        <v>553</v>
+      </c>
+      <c r="F188" s="1">
+        <v>765060.0</v>
       </c>
       <c r="G188" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H188" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I188" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J188" s="1" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="K188" s="1" t="s">
         <v>23</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M188" s="1" t="s">
         <v>27</v>
@@ -10419,10 +10428,10 @@
     </row>
     <row r="189">
       <c r="A189" s="2">
-        <v>765401.0</v>
+        <v>765400.0</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="C189" s="1">
         <v>10.0</v>
@@ -10431,10 +10440,10 @@
         <v>16</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="F189" s="1">
-        <v>765400.0</v>
+        <v>19</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="G189" s="1" t="s">
         <v>19</v>
@@ -10443,10 +10452,10 @@
         <v>27</v>
       </c>
       <c r="I189" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J189" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="K189" s="1" t="s">
         <v>23</v>
@@ -10463,10 +10472,10 @@
     </row>
     <row r="190">
       <c r="A190" s="2">
-        <v>765402.0</v>
+        <v>765401.0</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C190" s="1">
         <v>10.0</v>
@@ -10475,10 +10484,10 @@
         <v>16</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="F190" s="1">
-        <v>765401.0</v>
+        <v>765400.0</v>
       </c>
       <c r="G190" s="1" t="s">
         <v>19</v>
@@ -10487,10 +10496,10 @@
         <v>27</v>
       </c>
       <c r="I190" s="1" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="J190" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="K190" s="1" t="s">
         <v>23</v>
@@ -10507,10 +10516,10 @@
     </row>
     <row r="191">
       <c r="A191" s="2">
-        <v>714824.0</v>
+        <v>765402.0</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C191" s="1">
         <v>10.0</v>
@@ -10519,28 +10528,28 @@
         <v>16</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>19</v>
+        <v>581</v>
+      </c>
+      <c r="F191" s="1">
+        <v>765401.0</v>
       </c>
       <c r="G191" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="I191" s="1" t="s">
-        <v>139</v>
+        <v>534</v>
       </c>
       <c r="J191" s="1" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="K191" s="1" t="s">
-        <v>581</v>
-      </c>
-      <c r="L191" s="1">
-        <v>12.0</v>
+        <v>23</v>
+      </c>
+      <c r="L191" s="1" t="s">
+        <v>45</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>27</v>
@@ -10551,10 +10560,10 @@
     </row>
     <row r="192">
       <c r="A192" s="2">
-        <v>797253.0</v>
+        <v>714824.0</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C192" s="1">
         <v>10.0</v>
@@ -10563,19 +10572,19 @@
         <v>16</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>583</v>
+        <v>19</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="G192" s="1" t="s">
         <v>19</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="I192" s="1" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="J192" s="1" t="s">
         <v>584</v>
@@ -10583,8 +10592,8 @@
       <c r="K192" s="1" t="s">
         <v>585</v>
       </c>
-      <c r="L192" s="1" t="s">
-        <v>31</v>
+      <c r="L192" s="1">
+        <v>12.0</v>
       </c>
       <c r="M192" s="1" t="s">
         <v>27</v>
@@ -10595,7 +10604,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2">
-        <v>797256.0</v>
+        <v>797253.0</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>586</v>
@@ -10607,10 +10616,10 @@
         <v>16</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>208</v>
+        <v>587</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>587</v>
+        <v>336</v>
       </c>
       <c r="G193" s="1" t="s">
         <v>19</v>
@@ -10639,7 +10648,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2">
-        <v>710418.0</v>
+        <v>797256.0</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>590</v>
@@ -10651,10 +10660,10 @@
         <v>16</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>19</v>
+        <v>211</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>19</v>
+        <v>591</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>19</v>
@@ -10663,16 +10672,16 @@
         <v>27</v>
       </c>
       <c r="I194" s="1" t="s">
-        <v>121</v>
+        <v>161</v>
       </c>
       <c r="J194" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="K194" s="1" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="L194" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="M194" s="1" t="s">
         <v>27</v>
@@ -10683,10 +10692,10 @@
     </row>
     <row r="195">
       <c r="A195" s="2">
-        <v>711267.0</v>
+        <v>710418.0</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C195" s="1">
         <v>10.0</v>
@@ -10695,28 +10704,28 @@
         <v>16</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>594</v>
+        <v>19</v>
       </c>
       <c r="F195" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I195" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J195" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="G195" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H195" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I195" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="J195" s="1" t="s">
+      <c r="K195" s="1" t="s">
         <v>596</v>
       </c>
-      <c r="K195" s="1" t="s">
-        <v>597</v>
-      </c>
       <c r="L195" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="M195" s="1" t="s">
         <v>27</v>
@@ -10727,23 +10736,23 @@
     </row>
     <row r="196">
       <c r="A196" s="2">
-        <v>711291.0</v>
+        <v>711267.0</v>
       </c>
       <c r="B196" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="C196" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E196" s="1" t="s">
         <v>598</v>
       </c>
-      <c r="C196" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E196" s="1" t="s">
+      <c r="F196" s="1" t="s">
         <v>599</v>
       </c>
-      <c r="F196" s="1">
-        <v>711225.0</v>
-      </c>
       <c r="G196" s="1" t="s">
         <v>19</v>
       </c>
@@ -10751,13 +10760,13 @@
         <v>27</v>
       </c>
       <c r="I196" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J196" s="1" t="s">
-        <v>301</v>
+        <v>600</v>
       </c>
       <c r="K196" s="1" t="s">
-        <v>19</v>
+        <v>601</v>
       </c>
       <c r="L196" s="1" t="s">
         <v>50</v>
@@ -10774,7 +10783,7 @@
         <v>711227.0</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C197" s="1">
         <v>10.0</v>
@@ -10783,7 +10792,7 @@
         <v>16</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="F197" s="1">
         <v>711225.0</v>
@@ -10795,10 +10804,10 @@
         <v>27</v>
       </c>
       <c r="I197" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J197" s="1" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K197" s="1" t="s">
         <v>19</v>
@@ -10818,7 +10827,7 @@
         <v>715102.0</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="C198" s="1">
         <v>10.0</v>
@@ -10827,7 +10836,7 @@
         <v>16</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="F198" s="1">
         <v>715101.0</v>
@@ -10842,7 +10851,7 @@
         <v>21</v>
       </c>
       <c r="J198" s="1" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="K198" s="1" t="s">
         <v>23</v>
@@ -10859,10 +10868,10 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C199" s="1">
         <v>10.0</v>
@@ -10871,7 +10880,7 @@
         <v>16</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>19</v>
@@ -10886,10 +10895,10 @@
         <v>128</v>
       </c>
       <c r="J199" s="1" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="K199" s="1" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L199" s="1" t="s">
         <v>45</v>
@@ -10903,16 +10912,16 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="C200" s="1">
         <v>5.0</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>19</v>
@@ -10927,16 +10936,16 @@
         <v>27</v>
       </c>
       <c r="I200" s="1" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J200" s="1" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K200" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L200" s="1" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="M200" s="1" t="s">
         <v>27</v>
@@ -10947,40 +10956,40 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="C201" s="1">
         <v>10.0</v>
       </c>
       <c r="D201" s="1" t="s">
+        <v>617</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I201" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J201" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="K201" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L201" s="1" t="s">
         <v>614</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I201" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="J201" s="1" t="s">
-        <v>615</v>
-      </c>
-      <c r="K201" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L201" s="1" t="s">
-        <v>611</v>
       </c>
       <c r="M201" s="1" t="s">
         <v>27</v>
